--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView yWindow="3870" windowWidth="6140" windowHeight="4520"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -1198,8 +1198,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1210,8 +1210,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1225,6 +1255,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -1236,6 +1282,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1271,33 +1325,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1310,45 +1340,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1363,127 +1363,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1501,7 +1381,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1513,37 +1543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1554,15 +1554,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1577,6 +1568,56 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1600,21 +1641,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1628,32 +1654,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1662,145 +1662,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView yWindow="3870" windowWidth="6140" windowHeight="4520"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -450,7 +450,19 @@
     <t>SPD{0}アップ</t>
   </si>
   <si>
+    <t>Speed Up</t>
+  </si>
+  <si>
     <t>SPD{0}Up</t>
+  </si>
+  <si>
+    <t>速度ダウン</t>
+  </si>
+  <si>
+    <t>SPD{0}ダウン</t>
+  </si>
+  <si>
+    <t>Speed Down</t>
   </si>
   <si>
     <t>会心率アップ</t>
@@ -1196,10 +1208,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1207,57 +1219,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1277,6 +1238,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -1285,11 +1283,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1301,8 +1328,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1317,15 +1345,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1333,14 +1353,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1369,7 +1381,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1381,13 +1393,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1399,73 +1489,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1483,7 +1513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1495,7 +1525,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1507,43 +1555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1572,26 +1584,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1613,11 +1612,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1654,6 +1651,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1662,22 +1674,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -1686,121 +1698,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2127,7 +2139,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U90"/>
+  <dimension ref="A1:U91"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -3639,23 +3651,23 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="B23">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>会心率アップ</v>
+        <v>速度ダウン</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3680,16 +3692,16 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3702,19 +3714,19 @@
       </c>
       <c r="U23" t="str">
         <f>TextData!B23</f>
-        <v>会心率アップ</v>
+        <v>速度ダウン</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B24">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3748,16 +3760,16 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3770,19 +3782,19 @@
       </c>
       <c r="U24" t="str">
         <f>TextData!B24</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B25">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3816,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -3838,19 +3850,19 @@
       </c>
       <c r="U25" t="str">
         <f>TextData!B25</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B26">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3859,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3906,15 +3918,15 @@
       </c>
       <c r="U26" t="str">
         <f>TextData!B26</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B27">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
@@ -3949,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -3973,20 +3985,20 @@
         <v>1</v>
       </c>
       <c r="U27" t="str">
-        <f>TextData!B29</f>
-        <v>回避アップ</v>
+        <f>TextData!B27</f>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B28">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>命中ダウン</v>
+        <v>命中アップ</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4017,19 +4029,19 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -4042,19 +4054,19 @@
       </c>
       <c r="U28" t="str">
         <f>TextData!B30</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B29">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>命中ダウン</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4063,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4088,16 +4100,16 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -4109,20 +4121,20 @@
         <v>1</v>
       </c>
       <c r="U29" t="str">
-        <f>TextData!B29</f>
-        <v>回避アップ</v>
+        <f>TextData!B31</f>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B30">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4162,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -4178,19 +4190,19 @@
       </c>
       <c r="U30" t="str">
         <f>TextData!B30</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B31">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4221,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -4230,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -4246,35 +4258,35 @@
       </c>
       <c r="U31" t="str">
         <f>TextData!B31</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B32">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="str">
         <f>INDEX(Define!B:B,MATCH(G32,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -4289,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -4314,15 +4326,15 @@
       </c>
       <c r="U32" t="str">
         <f>TextData!B32</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B33">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
@@ -4385,32 +4397,32 @@
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="34" ht="12" customHeight="1" spans="1:21">
+    <row r="34" spans="1:21">
       <c r="A34">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="B34">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>火傷耐性</v>
+        <v>ダメージカット</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
         <f>INDEX(Define!B:B,MATCH(G34,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I34">
         <v>1</v>
@@ -4450,25 +4462,25 @@
       </c>
       <c r="U34" t="str">
         <f>TextData!B34</f>
-        <v>火傷耐性</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="B35">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>凍結耐性</v>
+        <v>火傷耐性</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -4518,25 +4530,25 @@
       </c>
       <c r="U35" t="str">
         <f>TextData!B35</f>
-        <v>凍結耐性</v>
+        <v>火傷耐性</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>1310</v>
+        <v>1220</v>
       </c>
       <c r="B36">
-        <v>1310</v>
+        <v>1220</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>炎耐性</v>
+        <v>凍結耐性</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F36" t="s">
         <v>32</v>
@@ -4586,25 +4598,25 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B36</f>
-        <v>炎耐性</v>
+        <v>凍結耐性</v>
       </c>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:21">
       <c r="A37">
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="B37">
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>雷耐性</v>
+        <v>炎耐性</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
@@ -4654,25 +4666,25 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B37</f>
-        <v>雷耐性</v>
+        <v>炎耐性</v>
       </c>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:21">
       <c r="A38">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="B38">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>氷耐性</v>
+        <v>雷耐性</v>
       </c>
       <c r="D38">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F38" t="s">
         <v>32</v>
@@ -4722,25 +4734,25 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B38</f>
-        <v>氷耐性</v>
+        <v>雷耐性</v>
       </c>
     </row>
     <row r="39" ht="12" customHeight="1" spans="1:21">
       <c r="A39">
-        <v>1340</v>
+        <v>1330</v>
       </c>
       <c r="B39">
-        <v>1340</v>
+        <v>1330</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>光耐性</v>
+        <v>氷耐性</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E39">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
         <v>32</v>
@@ -4790,25 +4802,25 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B39</f>
-        <v>光耐性</v>
+        <v>氷耐性</v>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1" spans="1:21">
       <c r="A40">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="B40">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>闇耐性</v>
+        <v>光耐性</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
         <v>32</v>
@@ -4858,25 +4870,25 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B40</f>
-        <v>闇耐性</v>
+        <v>光耐性</v>
       </c>
     </row>
     <row r="41" ht="12" customHeight="1" spans="1:21">
       <c r="A41">
-        <v>2010</v>
+        <v>1350</v>
       </c>
       <c r="B41">
-        <v>2010</v>
+        <v>1350</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>毒</v>
+        <v>闇耐性</v>
       </c>
       <c r="D41">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
         <v>32</v>
@@ -4892,10 +4904,10 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -4904,19 +4916,19 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -4926,18 +4938,19 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B41</f>
-        <v>毒</v>
+        <v>闇耐性</v>
       </c>
     </row>
     <row r="42" ht="12" customHeight="1" spans="1:21">
       <c r="A42">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B42">
         <v>2010</v>
       </c>
-      <c r="C42" t="s">
-        <v>34</v>
+      <c r="C42" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D42">
         <v>26</v>
@@ -4992,25 +5005,25 @@
         <v>1</v>
       </c>
       <c r="U42" t="str">
-        <f>TextData!B41</f>
+        <f>TextData!B42</f>
         <v>毒</v>
       </c>
     </row>
     <row r="43" ht="12" customHeight="1" spans="1:21">
       <c r="A43">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B43">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E43">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
         <v>32</v>
@@ -5060,47 +5073,46 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>火傷</v>
+        <v>毒</v>
       </c>
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:21">
       <c r="A44">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B44">
-        <v>2020</v>
-      </c>
-      <c r="C44" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2012</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
       </c>
       <c r="D44">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F44" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="str">
         <f>INDEX(Define!B:B,MATCH(G44,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I44">
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -5128,47 +5140,47 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="45" ht="12" customHeight="1" spans="1:21">
       <c r="A45">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B45">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E45">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" t="str">
         <f>INDEX(Define!B:B,MATCH(G45,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -5177,16 +5189,16 @@
         <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -5196,19 +5208,19 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B46">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -5227,10 +5239,10 @@
         <v>ターン数</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -5264,19 +5276,19 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B47">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -5285,14 +5297,14 @@
         <v>66</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="str">
         <f>INDEX(Define!B:B,MATCH(G47,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I47">
         <v>1</v>
@@ -5332,35 +5344,35 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B48">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -5400,41 +5412,41 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B49">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="F49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -5468,41 +5480,41 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B50">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50" t="str">
         <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -5536,28 +5548,28 @@
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B51">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5567,7 +5579,7 @@
         <v>ターン数</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="s">
         <v>20</v>
@@ -5604,35 +5616,35 @@
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B52">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="F52" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H52" t="str">
         <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5672,28 +5684,28 @@
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B53">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -5721,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53">
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5740,28 +5752,28 @@
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B54">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G54">
         <v>4</v>
@@ -5771,16 +5783,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -5789,13 +5801,13 @@
         <v>0</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54">
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -5808,47 +5820,47 @@
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B55">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>45</v>
+      </c>
+      <c r="G55">
         <v>4</v>
-      </c>
-      <c r="F55" t="s">
-        <v>47</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
       </c>
       <c r="H55" t="str">
         <f>INDEX(Define!B:B,MATCH(G55,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -5876,44 +5888,44 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B56">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
       <c r="D56">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5925,13 +5937,13 @@
         <v>0</v>
       </c>
       <c r="O56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56">
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -5944,44 +5956,44 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B57">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" t="str">
         <f>INDEX(Define!B:B,MATCH(G57,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57">
         <v>1</v>
@@ -6012,41 +6024,41 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B58">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58" t="str">
         <f>INDEX(Define!B:B,MATCH(G58,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>APカウント</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -6061,16 +6073,16 @@
         <v>0</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58">
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -6080,35 +6092,35 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B59">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H59" t="str">
         <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6144,32 +6156,32 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B60">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -6179,7 +6191,7 @@
         <v>ターン数</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -6212,32 +6224,32 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B61">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6247,7 +6259,7 @@
         <v>ターン数</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="s">
         <v>20</v>
@@ -6274,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -6284,38 +6296,38 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B62">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="str">
         <f>INDEX(Define!B:B,MATCH(G62,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="s">
         <v>20</v>
@@ -6342,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -6352,38 +6364,38 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B63">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H63" t="str">
         <f>INDEX(Define!B:B,MATCH(G63,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="s">
         <v>20</v>
@@ -6420,35 +6432,35 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B64">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" t="str">
         <f>INDEX(Define!B:B,MATCH(G64,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6488,28 +6500,28 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B65">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6556,28 +6568,28 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B66">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6624,38 +6636,38 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B67">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
+        <v>25</v>
+      </c>
+      <c r="F67" t="s">
         <v>21</v>
       </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
       <c r="G67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="str">
         <f>INDEX(Define!B:B,MATCH(G67,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="s">
         <v>20</v>
@@ -6667,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="M67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -6676,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -6692,35 +6704,35 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B68">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>56</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="str">
         <f>INDEX(Define!B:B,MATCH(G68,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I68">
         <v>1</v>
@@ -6735,7 +6747,7 @@
         <v>1</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -6744,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -6760,35 +6772,35 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B69">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>56</v>
-      </c>
-      <c r="F69" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="str">
         <f>INDEX(Define!B:B,MATCH(G69,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -6806,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -6828,28 +6840,28 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B70">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6896,19 +6908,19 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B71">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6917,7 +6929,7 @@
         <v>66</v>
       </c>
       <c r="F71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6964,28 +6976,28 @@
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B72">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7032,28 +7044,28 @@
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B73">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7100,25 +7112,25 @@
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B74">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F74" t="s">
         <v>61</v>
@@ -7168,28 +7180,28 @@
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B75">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7236,28 +7248,28 @@
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B76">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
       <c r="D76">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7282,19 +7294,19 @@
         <v>0</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76">
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -7304,28 +7316,28 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B77">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7372,19 +7384,19 @@
       </c>
       <c r="U77" t="str">
         <f>TextData!B76</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B78">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -7393,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7418,19 +7430,19 @@
         <v>0</v>
       </c>
       <c r="N78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -7440,19 +7452,19 @@
       </c>
       <c r="U78" t="str">
         <f>TextData!B77</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B79">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -7461,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7508,19 +7520,19 @@
       </c>
       <c r="U79" t="str">
         <f>TextData!B78</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B80">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -7529,14 +7541,14 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G80">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H80" t="str">
         <f>INDEX(Define!B:B,MATCH(G80,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -7569,26 +7581,26 @@
         <v>0</v>
       </c>
       <c r="S80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80">
         <v>1</v>
       </c>
       <c r="U80" t="str">
         <f>TextData!B79</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B81">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -7597,14 +7609,14 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
         <f>INDEX(Define!B:B,MATCH(G81,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -7634,29 +7646,29 @@
         <v>0</v>
       </c>
       <c r="R81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81">
         <v>1</v>
       </c>
       <c r="U81" t="str">
         <f>TextData!B80</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="82" spans="1:21">
       <c r="A82">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B82">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX(TextData!B:B,MATCH(B82,TextData!A:A))</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -7665,14 +7677,14 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82" t="str">
         <f>INDEX(Define!B:B,MATCH(G82,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -7712,19 +7724,19 @@
       </c>
       <c r="U82" t="str">
         <f>TextData!B81</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="83" spans="1:21">
       <c r="A83">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B83">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX(TextData!B:B,MATCH(B83,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -7733,14 +7745,14 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H83" t="str">
         <f>INDEX(Define!B:B,MATCH(G83,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I83">
         <v>1</v>
@@ -7770,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -7780,19 +7792,19 @@
       </c>
       <c r="U83" t="str">
         <f>TextData!B82</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="84" spans="1:21">
       <c r="A84">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B84">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX(TextData!B:B,MATCH(B84,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -7801,14 +7813,14 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H84" t="str">
         <f>INDEX(Define!B:B,MATCH(G84,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -7838,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="R84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -7848,35 +7860,35 @@
       </c>
       <c r="U84" t="str">
         <f>TextData!B83</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="85" spans="1:21">
       <c r="A85">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B85">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="C85" t="str">
         <f>INDEX(TextData!B:B,MATCH(B85,TextData!A:A))</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F85" t="s">
         <v>69</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H85" t="str">
         <f>INDEX(Define!B:B,MATCH(G85,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -7916,19 +7928,19 @@
       </c>
       <c r="U85" t="str">
         <f>TextData!B84</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="86" spans="1:21">
       <c r="A86">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B86">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="C86" t="str">
         <f>INDEX(TextData!B:B,MATCH(B86,TextData!A:A))</f>
-        <v>かばう無視</v>
+        <v>付与無効化</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -7974,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -7982,29 +7994,30 @@
       <c r="T86">
         <v>1</v>
       </c>
-      <c r="U86" t="s">
-        <v>70</v>
+      <c r="U86" t="str">
+        <f>TextData!B85</f>
+        <v>付与無効化</v>
       </c>
     </row>
     <row r="87" spans="1:21">
       <c r="A87">
-        <v>2500</v>
+        <v>2490</v>
       </c>
       <c r="B87">
-        <v>2500</v>
+        <v>2490</v>
       </c>
       <c r="C87" t="str">
         <f>INDEX(TextData!B:B,MATCH(B87,TextData!A:A))</f>
-        <v>ダメージカット無効</v>
+        <v>かばう無視</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="F87" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -8035,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -8049,30 +8062,29 @@
       <c r="T87">
         <v>1</v>
       </c>
-      <c r="U87" t="str">
-        <f>TextData!B86</f>
-        <v>ダメージカット無効</v>
+      <c r="U87" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:21">
       <c r="A88">
-        <v>3010</v>
+        <v>2500</v>
       </c>
       <c r="B88">
-        <v>3010</v>
+        <v>2500</v>
       </c>
       <c r="C88" t="str">
         <f>INDEX(TextData!B:B,MATCH(B88,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>ダメージカット無効</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -8097,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -8119,19 +8131,19 @@
       </c>
       <c r="U88" t="str">
         <f>TextData!B87</f>
-        <v>チャージ</v>
+        <v>ダメージカット無効</v>
       </c>
     </row>
     <row r="89" spans="1:21">
       <c r="A89">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B89">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C89" t="str">
         <f>INDEX(TextData!B:B,MATCH(B89,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8187,19 +8199,19 @@
       </c>
       <c r="U89" t="str">
         <f>TextData!B88</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
     </row>
     <row r="90" spans="1:21">
       <c r="A90">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B90">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="C90" t="str">
         <f>INDEX(TextData!B:B,MATCH(B90,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>リンケージ</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -8255,6 +8267,74 @@
       </c>
       <c r="U90" t="str">
         <f>TextData!B89</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
+      <c r="A91">
+        <v>9999</v>
+      </c>
+      <c r="B91">
+        <v>9999</v>
+      </c>
+      <c r="C91" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B91,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>61</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="str">
+        <f>INDEX(Define!B:B,MATCH(G91,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>1</v>
+      </c>
+      <c r="U91" t="str">
+        <f>TextData!B90</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -8268,7 +8348,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -8645,32 +8725,32 @@
         <v>143</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" t="s">
         <v>145</v>
-      </c>
-      <c r="C23" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B24" t="s">
         <v>149</v>
@@ -8687,7 +8767,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B25" t="s">
         <v>153</v>
@@ -8704,7 +8784,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B26" t="s">
         <v>157</v>
@@ -8721,24 +8801,24 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B28" t="s">
         <v>161</v>
@@ -8755,7 +8835,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B29" t="s">
         <v>165</v>
@@ -8772,7 +8852,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B30" t="s">
         <v>169</v>
@@ -8789,67 +8869,67 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F33" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="B34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" t="s">
         <v>179</v>
-      </c>
-      <c r="C34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F34" t="s">
-        <v>181</v>
       </c>
       <c r="G34" t="s">
         <v>182</v>
@@ -8857,7 +8937,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="B35" t="s">
         <v>183</v>
@@ -8866,32 +8946,32 @@
         <v>184</v>
       </c>
       <c r="F35" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>1310</v>
+        <v>1220</v>
       </c>
       <c r="B36" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s">
         <v>185</v>
       </c>
-      <c r="C36" t="s">
+      <c r="G36" t="s">
         <v>186</v>
-      </c>
-      <c r="F36" t="s">
-        <v>187</v>
-      </c>
-      <c r="G36" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="B37" t="s">
         <v>189</v>
@@ -8908,7 +8988,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="B38" t="s">
         <v>193</v>
@@ -8925,7 +9005,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>1340</v>
+        <v>1330</v>
       </c>
       <c r="B39" t="s">
         <v>197</v>
@@ -8942,7 +9022,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>1350</v>
+        <v>1340</v>
       </c>
       <c r="B40" t="s">
         <v>201</v>
@@ -8959,58 +9039,58 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>2010</v>
+        <v>1350</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G42" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" t="s">
         <v>209</v>
       </c>
-      <c r="C43" t="s">
-        <v>210</v>
-      </c>
       <c r="F43" t="s">
+        <v>212</v>
+      </c>
+      <c r="G43" t="s">
         <v>211</v>
-      </c>
-      <c r="G43" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B44" t="s">
         <v>213</v>
@@ -9027,7 +9107,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B45" t="s">
         <v>217</v>
@@ -9044,7 +9124,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B46" t="s">
         <v>221</v>
@@ -9061,7 +9141,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B47" t="s">
         <v>225</v>
@@ -9078,7 +9158,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B48" t="s">
         <v>229</v>
@@ -9095,7 +9175,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B49" t="s">
         <v>233</v>
@@ -9112,7 +9192,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B50" t="s">
         <v>237</v>
@@ -9129,7 +9209,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B51" t="s">
         <v>241</v>
@@ -9146,7 +9226,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B52" t="s">
         <v>245</v>
@@ -9163,7 +9243,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B53" t="s">
         <v>249</v>
@@ -9180,7 +9260,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B54" t="s">
         <v>253</v>
@@ -9197,7 +9277,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B55" t="s">
         <v>257</v>
@@ -9206,41 +9286,41 @@
         <v>258</v>
       </c>
       <c r="F55" t="s">
-        <v>48</v>
+        <v>259</v>
       </c>
       <c r="G55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G56" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B57" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F57" t="s">
-        <v>265</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
         <v>266</v>
@@ -9248,7 +9328,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B58" t="s">
         <v>267</v>
@@ -9265,7 +9345,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B59" t="s">
         <v>271</v>
@@ -9282,7 +9362,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B60" t="s">
         <v>275</v>
@@ -9299,7 +9379,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B61" t="s">
         <v>279</v>
@@ -9316,7 +9396,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B62" t="s">
         <v>283</v>
@@ -9333,7 +9413,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B63" t="s">
         <v>287</v>
@@ -9350,7 +9430,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B64" t="s">
         <v>291</v>
@@ -9367,7 +9447,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B65" t="s">
         <v>295</v>
@@ -9384,7 +9464,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B66" t="s">
         <v>299</v>
@@ -9401,7 +9481,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B67" t="s">
         <v>303</v>
@@ -9418,7 +9498,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B68" t="s">
         <v>307</v>
@@ -9435,7 +9515,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B69" t="s">
         <v>311</v>
@@ -9452,7 +9532,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B70" t="s">
         <v>315</v>
@@ -9469,7 +9549,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B71" t="s">
         <v>319</v>
@@ -9486,7 +9566,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B72" t="s">
         <v>323</v>
@@ -9503,7 +9583,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B73" t="s">
         <v>327</v>
@@ -9520,7 +9600,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B74" t="s">
         <v>331</v>
@@ -9529,24 +9609,24 @@
         <v>332</v>
       </c>
       <c r="F74" t="s">
-        <v>62</v>
+        <v>333</v>
       </c>
       <c r="G74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F75" t="s">
-        <v>336</v>
+        <v>62</v>
       </c>
       <c r="G75" t="s">
         <v>337</v>
@@ -9554,7 +9634,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B76" t="s">
         <v>338</v>
@@ -9571,7 +9651,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B77" t="s">
         <v>342</v>
@@ -9580,24 +9660,24 @@
         <v>343</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>344</v>
       </c>
       <c r="G77" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B78" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C78" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F78" t="s">
-        <v>347</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
         <v>348</v>
@@ -9605,7 +9685,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B79" t="s">
         <v>349</v>
@@ -9622,7 +9702,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B80" t="s">
         <v>353</v>
@@ -9639,7 +9719,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B81" t="s">
         <v>357</v>
@@ -9656,7 +9736,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B82" t="s">
         <v>361</v>
@@ -9673,7 +9753,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B83" t="s">
         <v>365</v>
@@ -9682,24 +9762,24 @@
         <v>366</v>
       </c>
       <c r="F83" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="G83" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B84" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C84" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F84" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="G84" t="s">
         <v>371</v>
@@ -9707,33 +9787,33 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>372</v>
       </c>
       <c r="C85" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F85" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G85" t="s">
-        <v>20</v>
+        <v>375</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>2500</v>
+        <v>2490</v>
       </c>
       <c r="B86" t="s">
-        <v>373</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
+        <v>376</v>
+      </c>
+      <c r="F86" t="s">
         <v>374</v>
-      </c>
-      <c r="F86" t="s">
-        <v>309</v>
       </c>
       <c r="G86" t="s">
         <v>20</v>
@@ -9741,24 +9821,24 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>3010</v>
+        <v>2500</v>
       </c>
       <c r="B87" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C87" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F87" t="s">
-        <v>377</v>
+        <v>313</v>
       </c>
       <c r="G87" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B88" t="s">
         <v>379</v>
@@ -9775,18 +9855,35 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B89" t="s">
         <v>383</v>
       </c>
       <c r="C89" t="s">
+        <v>384</v>
+      </c>
+      <c r="F89" t="s">
+        <v>385</v>
+      </c>
+      <c r="G89" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>9999</v>
+      </c>
+      <c r="B90" t="s">
+        <v>387</v>
+      </c>
+      <c r="C90" t="s">
         <v>20</v>
       </c>
-      <c r="F89" t="s">
-        <v>383</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="F90" t="s">
+        <v>387</v>
+      </c>
+      <c r="G90" t="s">
         <v>20</v>
       </c>
     </row>
@@ -9812,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9820,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9828,7 +9925,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9836,7 +9933,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9844,7 +9941,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9852,7 +9949,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9860,7 +9957,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -1208,10 +1208,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1223,8 +1223,23 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1235,6 +1250,14 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1253,6 +1276,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1262,24 +1292,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1299,45 +1337,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1358,13 +1365,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1375,13 +1375,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1393,13 +1399,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1417,145 +1555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1566,6 +1566,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1580,17 +1604,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1613,6 +1626,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -1621,33 +1643,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1674,145 +1674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -1209,9 +1209,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1223,7 +1223,113 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1246,83 +1352,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1330,39 +1360,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1375,19 +1375,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1399,7 +1453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1411,61 +1477,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1477,49 +1495,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1537,25 +1519,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1566,30 +1566,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1608,6 +1584,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1619,24 +1604,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1666,6 +1633,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1674,25 +1674,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1701,118 +1701,118 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
